--- a/data/daily/2026-10/2026-10-03.xlsx
+++ b/data/daily/2026-10/2026-10-03.xlsx
@@ -1170,14 +1170,89 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,160 +1267,85 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>3</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1425,182 +1425,182 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -2596,31 +2596,27 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16207</v>
+        <v>16208</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>고급스러운 선물 포장 — 포장이 깔끔하고 예뻐 선물용으로 만족도가 매우 높음</t>
+          <t>피로 해소 및 활력 증진 — 섭취 후 피로가 풀리고 기력이 돋는 효과를 느낌</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>피로 회복 및 활력 체감 — 한 병씩 복용할 때마다 피로가 확 풀리고 기운이 솟는 느낌을 받음</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>간편한 휴대 및 섭취 — 작고 가벼워 가방에 하나씩 넣어 휴대하며 챙겨 먹기 편함</t>
-        </is>
-      </c>
+          <t>선물용으로 뛰어난 포장 — 깔끔하고 예쁜 포장 디자인으로 선물 시 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>짧은 잔여 유통기한 — 수령일 기준 유통기한이 10개월 미만으로 남아 보관하며 천천히 먹기에 아쉬움</t>
+          <t>짧은 유통기한 — 유통기한이 10개월 미만으로 남은 제품이 배송됨</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>작은 제품 크기 — 손바닥 정도의 작은 상자 크기로 선물용 외관 부피가 작음</t>
+          <t>작은 제품 크기 — 손바닥 정도의 작은 크기로 선물용 볼륨감이 아쉬움</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -2663,24 +2659,20 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15523</v>
+        <v>15524</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>깔끔하고 예쁜 패키지 — 상자 포장이 예쁘고 고급스러워 명절이나 생일 선물용으로 인기가 좋음</t>
+          <t>간편한 영양 충전 — 다양한 비타민과 미네랄을 한 번에 간편하게 챙김</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 복합 영양 섭취 — 다양한 비타민과 미네랄을 한 번에 간단하게 챙겨 먹기 편리함</t>
+          <t>깔끔한 패키지 박스 — 패키지 박스가 예쁘고 깔끔하여 선물용으로 좋음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>배송 지연 발생 — 사전 안내 연락은 있었으나 배송 일정이 다소 지연되어 도착함</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
@@ -2726,25 +2718,21 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>품격 있는 선물 포장 — 고급스러운 기프트 에디션 포장으로 선물 전달 시 만족도가 높음</t>
+          <t>우수한 피로 회복 효과 — 섭취 후 피로 해소 및 건강 관리에 도움을 받음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>피로 회복 및 건강 관리 — 복용 시 피로가 풀리고 감기 예방 등 전반적인 컨디션 관리에 도움됨</t>
+          <t>고급스러운 선물 포장 — 포장이 깔끔하고 고급스러워 선물용으로 제격임</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>보낸 사람 확인 불가 — 발송인 정보가 명확히 확인되지 않고 고객 문의 응대가 미흡함</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>부담스러운 정가 가격 — 정상 판매 가격대가 다소 높아 할인 기간에 주로 구매하게 됨</t>
-        </is>
-      </c>
+          <t>보낸 사람 확인 불가 — 선물 발송인 확인이 어렵고 문의 응대가 부족함</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
@@ -2789,12 +2777,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>맛있는 과일맛 젤리 — 새콤달콤한 과일 향이 가득하여 약이 아닌 간식처럼 맛있게 먹기 좋음</t>
+          <t>맛있는 젤리 형태 — 새콤달콤한 과일향과 쫄깃한 식감으로 맛이 뛰어남</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>편안한 목넘김과 식감 — 알약 삼킴이 어렵거나 수술 후 목넘김이 힘들 때도 씹어서 편하게 섭취 가능함</t>
+          <t>쉽고 편리한 섭취 방식 — 알약을 잘 삼키지 못해도 씹어서 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -2844,18 +2832,18 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>기력 회복 및 피로 개선 — 자기 전 복용 시 다음 날 아침 피로가 덜하고 기력 회복에 도움됨</t>
+          <t>체감되는 기력 회복 — 섭취 시 피로 해소 및 기력 회복에 도움을 느낌</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>알찬 단독 에디션 구성 — 본품 7입에 2입 추가 증정 및 정제와 액상 복합 제형으로 구성이 실속 있음</t>
+          <t>알찬 추가 증정 구성 — 추가 증정 구성이 포함되어 알차고 간편하게 챙기기 좋음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>다소 아쉬운 소포장 부피 — 소포장 제품 특성상 겉보기에 선물이 풍성해 보이지는 않음</t>
+          <t>작아 보이는 선물 규모 — 소포장 제품이라 선물 외관이 풍성해 보이지 않음</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -2899,16 +2887,16 @@
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>고급스러운 명절 포장 — 고급 박스와 종이가방이 함께 제공되어 귀한 명절 선물로 전달하기 적합함</t>
+          <t>고급스러운 명절 선물 — 고급 박스와 종이가방 구성으로 명절 선물용으로 좋음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>빠른 기력 충전 효과 — 지치고 피곤할 때 복용 후 기운을 차리는 데 뚜렷한 도움을 받음</t>
+          <t>빠른 활력 충전 — 피로가 누적되었을 때 섭취하여 활력을 회복함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -2958,18 +2946,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>간편한 휴대 및 복용 — 한 병씩 들고 다니며 사무실 등에서 물 없이 간편하게 섭취 가능함</t>
+          <t>뛰어난 휴대성 — 간편하게 들고 다니며 어디서나 먹기 편함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>가성비와 빠른 배송 — 배송이 신속하며 타사 유명 이뮨 비타민 대비 가격대가 합리적임</t>
+          <t>하루 활력 증진 — 아침 복용 시 하루 에너지를 채우는 데 도움이 됨</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>높은 당류 함유량 우려 — 한 병당 당류가 4g 함유되어 있어 액상과당 섭취에 부담감을 느낌</t>
+          <t>높은 당 함량 — 당 함량이 4g 포함되어 액상과당 성분이 다소 부담스러움</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -3013,26 +3001,22 @@
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 구성 — 패키지가 고급스럽고 종이봉투가 동봉되어 선물용으로 매우 만족스러움</t>
+          <t>쓰지 않고 달콤한 맛 — 쓴맛 없이 달콤하여 거부감 없이 맛있게 먹음</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>쓰지 않은 달콤한 맛 — 약재 특유의 쓴맛 없이 달달하여 어르신이나 남녀노소 먹기 수월함</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>물 없는 간편한 섭취 — 가루와 액상을 뚜껑으로 섞어 물 없이 바로 마실 수 있어 편리함</t>
-        </is>
-      </c>
+          <t>고급스러운 패키지 — 패키지 외관이 고급스러워 선물용으로 인기가 높음</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>뚜껑 개봉의 어려움 — 손 힘이 약한 경우 뚜껑을 눌러 분말을 터뜨리고 여는 과정이 뻑뻑함</t>
+          <t>열기 힘든 용기 뚜껑 — 손 힘이 약하면 용기 뚜껑을 개봉하기 다소 힘듦</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -3080,18 +3064,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>성별 맞춤 옵션 선택 — 남성과 여성에게 필요한 영양 설계를 각각 선택하여 선물할 수 있음</t>
+          <t>성별 맞춤 옵션 — 남성과 여성용으로 세분화되어 있어 맞춤 선택 가능함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>지속적인 활력 체감 — 꾸준히 복용 시 피로가 덜하고 개운한 컨디션이 오래 지속됨</t>
+          <t>쓴맛 없는 간편 섭취 — 쓴맛이 없고 휴대와 복용이 매우 편리함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>큰 알약 크기의 삼킴 부담 — 기존 제품 대비 알약 크기가 커서 한 번에 삼키기 다소 버거움</t>
+          <t>부담스러운 알약 크기 — 동봉된 알약 크기가 커서 삼키기 다소 불편함</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -3139,18 +3123,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>고함량 비타민C 보충 — 한 포당 3,000mg의 고함량 과립형 비타민C로 충분한 흡수를 기대할 수 있음</t>
+          <t>높은 비타민C 함량 — 3000mg 고함량 과립형이라 영양 흡수에 용이함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>빠른 활력 및 개운함 — 섭취 후 피로감이 가시고 정신이 확 들며 개운해지는 기분을 느낌</t>
+          <t>빠른 피로 회복 — 섭취 후 정신이 개운해지고 피로 해소에 도움이 됨</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>강한 신맛의 자극 — 고함량 비타민C 분말 특성상 생각보다 신맛이 강해 먹을 때 찌릿함</t>
+          <t>강한 신맛 — 분말 제형 특성상 강한 신맛이 느껴짐</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -3194,16 +3178,16 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>맛있는 소다맛 풍미 — 달지 않고 시원한 뽕따 소다 맛으로 거부감 없이 단독 섭취하기 좋음</t>
+          <t>상큼하고 맛있는 풍미 — 블루베리요거트 및 소다 맛 등 상큼하게 먹기 좋음</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>아이돌 포토카드 굿즈 — 아이돌 콜라보 포토카드 등 특별한 구성품이 포함되어 소장 가치가 높음</t>
+          <t>만족스러운 굿즈 구성 — 함께 제공되는 포토카드와 엽서 구성의 만족도가 높음</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -3249,23 +3233,19 @@
         <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>식후 소화 개선 효과 — 밀가루나 탄수화물 섭취 후 복용 시 속 더부룩함이 완화되고 편안해짐</t>
+          <t>편안한 소화 작용 — 식후 섭취 시 속이 편해지고 소화에 도움을 받음</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>구수한 고구마맛 풍미 — 거부감 없는 구수한 고구마 맛이라 남녀노소 누구나 먹기 편함</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>알찬 사은품 추가 증정 — 파로 곡물바와 파인키위효소 등 추가 증정품 구성이 푸짐함</t>
-        </is>
-      </c>
+          <t>구수한 고구마 맛 — 구수한 고구마 풍미로 거부감 없이 맛있게 복용함</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -3312,18 +3292,18 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>우아한 선물 포장 — 플리츠백과 보자기 에디션 포장이 고급스러워 선물용으로 만족도가 높음</t>
+          <t>고급스러운 포장 디자인 — 플리츠백 등 고급스러운 패키지 구성으로 만족스러움</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>거부감 없는 맛과 피로 개선 — 비린 맛 없이 달콤하게 마시기 좋으며 피로 완화에도 도움됨</t>
+          <t>체감되는 피로 개선 — 꾸준히 마셨을 때 피로감이 덜 느껴짐</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>비싼 가격대 부담 — 제품 단가가 다소 높아 할인 행사가 없을 때는 구매 부담이 큼</t>
+          <t>부담스러운 가격 — 가격대가 다소 높아 할인 시에 주로 구매하게 됨</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -3371,23 +3351,23 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 포만감 — 닭가슴살 특유의 물림 없이 맛있으며 한 개만 먹어도 포만감이 큼</t>
+          <t>뛰어난 맛과 포만감 — 한 개만 먹어도 포만감이 높고 소스가 맛있음</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>다채로운 맛과 보냉백 증정 — 30팩의 다양한 종류로 식단 구성이 좋고 증정 보냉백 디자인이 예쁨</t>
+          <t>다양한 식단 구성 — 종류가 다양하여 매일 질리지 않고 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>포장 불량 및 소스 누출 — 진공포장이 헐겁거나 배송 중 팩이 터져 소스가 새어 나오는 경우가 있음</t>
+          <t>구성품 오배송 — 주문한 구성과 다르게 종류가 중복되거나 누락 배송됨</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>오배송 및 문의 응대 미흡 — 주문 구성과 다른 제품이 중복 배송되었으나 판매자 응대가 원활하지 않음</t>
+          <t>제품 포장 파손 — 배송 중 포장이 터져 소스가 새거나 밀봉이 느슨함</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -3434,18 +3414,18 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>부드럽고 촉촉한 식감 — 퍽퍽하지 않고 육질이 매우 부드러우며 잡내가 나지 않아 질리지 않음</t>
+          <t>부드럽고 촉촉한 식감 — 잡내가 없고 퍽퍽하지 않아 부드럽게 섭취 가능함</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>알찬 구성과 뛰어난 가성비 — 다양한 종류의 닭가슴살과 간식을 할인된 저렴한 가격에 구매 가능함</t>
+          <t>우수한 가격 경쟁력 — 다양한 구성 대비 할인 가격이 저렴하여 가성비가 훌륭함</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>선호 품목 제외 아쉬움 — 가장 선호하는 파우치형 그릴 제품이 이번 구성에 빠져 있어 아쉬움</t>
+          <t>선호 구성의 부재 — 가장 맛있는 파우치형 그릴 제품이 포함되지 않아 아쉬움</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -3462,47 +3442,51 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
+          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>28,900원</t>
+          <t>20,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/10848340</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20241128105752_bb00bdfb255b4aad91bbff59ec2c2cfd.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>217</v>
+        <v>69</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>비린내 없는 깔끔한 맛 — 프로틴 음료 특유의 텁텁함과 비린 맛 없이 진한 초코우유처럼 달콤함</t>
+          <t>쫄깃하고 촉촉한 식감 — 부드럽고 촉촉하여 다이어트 중에도 맛있게 섭취함</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>든든한 운동 후 단백질 보충 — 운동 직후 간편하게 마시기 좋으며 포만감이 오래 유지됨</t>
+          <t>전자레인지 조리 간편성 — 전자레인지로 쉽게 데워 먹을 수 있어 조리가 편함</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>다소 느린 배송 — 주문 후 제품을 받아보기까지 배송 시간이 조금 걸림</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
     </row>
@@ -3517,51 +3501,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20,900원</t>
+          <t>28,900원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10848340</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20241128105752_bb00bdfb255b4aad91bbff59ec2c2cfd.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907094509_48a662610e174029823081c612ed4755.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>촉촉하고 쫄깃한 식감 — 퍽퍽함 없이 육질이 촉촉하고 부드러워 다이어트 중에도 맛있게 섭취함</t>
+          <t>비린 맛 없는 달콤함 — 단백질 특유의 비리고 텁텁한 맛이 없어 마시기 편함</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>간편한 조리 및 섭취 — 전자레인지로 빠르게 조리 가능하며 한입 크기 볼 형태라 샐러드 곁들임에 좋음</t>
+          <t>운동 후 든든한 포만감 — 운동 후 섭취 시 포만감을 주어 허기짐을 줄여줌</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>다소 아쉬운 배송 속도 — 주문 후 출고 및 배송 도착까지 시간이 다소 걸림</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
     </row>
@@ -3607,19 +3587,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>초고함량 활력 개선 효과 — 6,200mg 초고함량 아르기닌으로 운동 시 체력과 일상 활력 증진에 도움됨</t>
+          <t>체감되는 활력 증진 — 섭취 후 피로감이 줄고 운동 퍼포먼스 및 체력 유지에 도움 됨</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>간편한 1일 1포 스틱 — 개별 포장된 액상 스틱 형태로 하루 한 포 간편하게 휴대하며 복용 가능함</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>고급스러운 전용 쇼핑백 — 블랙과 레드의 깔끔한 포장과 전용 쇼핑백 증정으로 선물하기에 적합함</t>
-        </is>
-      </c>
+          <t>고함량 스틱 포장 — 1포당 함량이 높고 개별 포장되어 휴대가 간편함</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -3635,55 +3611,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>알디콤</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>33,200원</t>
+          <t>21,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12064702</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>21</v>
+        <v>903</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 체감 — 음주 전후 복용 시 다음 날 아침 두통과 피로감이 덜해 숙취 해소에 탁월함</t>
+          <t>변비 완화 및 가벼움 — 복용 후 배변 활동이 원활해지고 몸이 가벼워짐</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>휴대 편한 액상 스틱 — 물 없이 바로 짜먹을 수 있는 21ml 소용량 스틱이라 술자리 휴대에 적합함</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>고급스러운 선물세트 패키지 — 보라색 쇼핑백과 리본 손잡이가 달린 포장으로 애주가 선물용으로 좋음</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>약재 특유의 한약맛 — 쌍화탕이나 헛개 농축액 같은 씁쓸한 한약 맛이 돌아 입맛에 따라 호불호가 갈림</t>
-        </is>
-      </c>
+          <t>저렴한 가격과 사은품 — 가격이 저렴하고 증정 과자 등 사은품 구성이 좋음</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
     </row>
@@ -3698,47 +3666,51 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+          <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>알디콤</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>21,900원</t>
+          <t>33,200원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/12064702</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827134326_6543fa160cfd4c4294103fd47b3d0a12.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>903</v>
+        <v>21</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>속 편안함 및 배변 도움 — 식후 복용 시 더부룩한 속이 편안해지고 배변 활동이 원활해짐을 느낌</t>
+          <t>탁월한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 숙취와 피로감이 줄어듦</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>착한 가격과 스낵 증정 — 100포 대용량을 저렴하게 구매할 수 있고 저당 씬칩 사은품도 만족스러움</t>
+          <t>고급스러운 선물 패키지 — 쇼핑백과 스틱 포장이 고급스러워 선물용으로 적합함</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>한약재 풍미의 호불호 — 쌍화탕이나 한약재 특유의 맛이 나 호불호가 갈릴 수 있음</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
     </row>
@@ -4060,10 +4032,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16207</v>
+        <v>16208</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15523</v>
+        <v>15524</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3389</v>
@@ -4075,13 +4047,13 @@
         <v>8740</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>807</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>778</v>
@@ -4090,7 +4062,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="8" ht="90" customHeight="1">
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -4098,64 +4070,62 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 선물 포장 — 포장이 깔끔하고 예뻐 선물용으로 만족도가 매우 높음
-피로 회복 및 활력 체감 — 한 병씩 복용할 때마다 피로가 확 풀리고 기운이 솟는 느낌을 받음
-간편한 휴대 및 섭취 — 작고 가벼워 가방에 하나씩 넣어 휴대하며 챙겨 먹기 편함</t>
+          <t>피로 해소 및 활력 증진 — 섭취 후 피로가 풀리고 기력이 돋는 효과를 느낌
+선물용으로 뛰어난 포장 — 깔끔하고 예쁜 포장 디자인으로 선물 시 만족도가 높음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>깔끔하고 예쁜 패키지 — 상자 포장이 예쁘고 고급스러워 명절이나 생일 선물용으로 인기가 좋음
-간편한 복합 영양 섭취 — 다양한 비타민과 미네랄을 한 번에 간단하게 챙겨 먹기 편리함</t>
+          <t>간편한 영양 충전 — 다양한 비타민과 미네랄을 한 번에 간편하게 챙김
+깔끔한 패키지 박스 — 패키지 박스가 예쁘고 깔끔하여 선물용으로 좋음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>품격 있는 선물 포장 — 고급스러운 기프트 에디션 포장으로 선물 전달 시 만족도가 높음
-피로 회복 및 건강 관리 — 복용 시 피로가 풀리고 감기 예방 등 전반적인 컨디션 관리에 도움됨</t>
+          <t>우수한 피로 회복 효과 — 섭취 후 피로 해소 및 건강 관리에 도움을 받음
+고급스러운 선물 포장 — 포장이 깔끔하고 고급스러워 선물용으로 제격임</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 과일맛 젤리 — 새콤달콤한 과일 향이 가득하여 약이 아닌 간식처럼 맛있게 먹기 좋음
-편안한 목넘김과 식감 — 알약 삼킴이 어렵거나 수술 후 목넘김이 힘들 때도 씹어서 편하게 섭취 가능함</t>
+          <t>맛있는 젤리 형태 — 새콤달콤한 과일향과 쫄깃한 식감으로 맛이 뛰어남
+쉽고 편리한 섭취 방식 — 알약을 잘 삼키지 못해도 씹어서 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>기력 회복 및 피로 개선 — 자기 전 복용 시 다음 날 아침 피로가 덜하고 기력 회복에 도움됨
-알찬 단독 에디션 구성 — 본품 7입에 2입 추가 증정 및 정제와 액상 복합 제형으로 구성이 실속 있음</t>
+          <t>체감되는 기력 회복 — 섭취 시 피로 해소 및 기력 회복에 도움을 느낌
+알찬 추가 증정 구성 — 추가 증정 구성이 포함되어 알차고 간편하게 챙기기 좋음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 명절 포장 — 고급 박스와 종이가방이 함께 제공되어 귀한 명절 선물로 전달하기 적합함
-빠른 기력 충전 효과 — 지치고 피곤할 때 복용 후 기운을 차리는 데 뚜렷한 도움을 받음</t>
+          <t>고급스러운 명절 선물 — 고급 박스와 종이가방 구성으로 명절 선물용으로 좋음
+빠른 활력 충전 — 피로가 누적되었을 때 섭취하여 활력을 회복함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>간편한 휴대 및 복용 — 한 병씩 들고 다니며 사무실 등에서 물 없이 간편하게 섭취 가능함
-가성비와 빠른 배송 — 배송이 신속하며 타사 유명 이뮨 비타민 대비 가격대가 합리적임</t>
+          <t>뛰어난 휴대성 — 간편하게 들고 다니며 어디서나 먹기 편함
+하루 활력 증진 — 아침 복용 시 하루 에너지를 채우는 데 도움이 됨</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 구성 — 패키지가 고급스럽고 종이봉투가 동봉되어 선물용으로 매우 만족스러움
-쓰지 않은 달콤한 맛 — 약재 특유의 쓴맛 없이 달달하여 어르신이나 남녀노소 먹기 수월함
-물 없는 간편한 섭취 — 가루와 액상을 뚜껑으로 섞어 물 없이 바로 마실 수 있어 편리함</t>
+          <t>쓰지 않고 달콤한 맛 — 쓴맛 없이 달콤하여 거부감 없이 맛있게 먹음
+고급스러운 패키지 — 패키지 외관이 고급스러워 선물용으로 인기가 높음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>성별 맞춤 옵션 선택 — 남성과 여성에게 필요한 영양 설계를 각각 선택하여 선물할 수 있음
-지속적인 활력 체감 — 꾸준히 복용 시 피로가 덜하고 개운한 컨디션이 오래 지속됨</t>
+          <t>성별 맞춤 옵션 — 남성과 여성용으로 세분화되어 있어 맞춤 선택 가능함
+쓴맛 없는 간편 섭취 — 쓴맛이 없고 휴대와 복용이 매우 편리함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>고함량 비타민C 보충 — 한 포당 3,000mg의 고함량 과립형 비타민C로 충분한 흡수를 기대할 수 있음
-빠른 활력 및 개운함 — 섭취 후 피로감이 가시고 정신이 확 들며 개운해지는 기분을 느낌</t>
+          <t>높은 비타민C 함량 — 3000mg 고함량 과립형이라 영양 흡수에 용이함
+빠른 피로 회복 — 섭취 후 정신이 개운해지고 피로 해소에 도움이 됨</t>
         </is>
       </c>
     </row>
@@ -4167,46 +4137,41 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>짧은 잔여 유통기한 — 수령일 기준 유통기한이 10개월 미만으로 남아 보관하며 천천히 먹기에 아쉬움
-작은 제품 크기 — 손바닥 정도의 작은 상자 크기로 선물용 외관 부피가 작음</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>배송 지연 발생 — 사전 안내 연락은 있었으나 배송 일정이 다소 지연되어 도착함</t>
-        </is>
-      </c>
+          <t>짧은 유통기한 — 유통기한이 10개월 미만으로 남은 제품이 배송됨
+작은 제품 크기 — 손바닥 정도의 작은 크기로 선물용 볼륨감이 아쉬움</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>보낸 사람 확인 불가 — 발송인 정보가 명확히 확인되지 않고 고객 문의 응대가 미흡함
-부담스러운 정가 가격 — 정상 판매 가격대가 다소 높아 할인 기간에 주로 구매하게 됨</t>
+          <t>보낸 사람 확인 불가 — 선물 발송인 확인이 어렵고 문의 응대가 부족함</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>다소 아쉬운 소포장 부피 — 소포장 제품 특성상 겉보기에 선물이 풍성해 보이지는 않음</t>
+          <t>작아 보이는 선물 규모 — 소포장 제품이라 선물 외관이 풍성해 보이지 않음</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>높은 당류 함유량 우려 — 한 병당 당류가 4g 함유되어 있어 액상과당 섭취에 부담감을 느낌</t>
+          <t>높은 당 함량 — 당 함량이 4g 포함되어 액상과당 성분이 다소 부담스러움</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>뚜껑 개봉의 어려움 — 손 힘이 약한 경우 뚜껑을 눌러 분말을 터뜨리고 여는 과정이 뻑뻑함</t>
+          <t>열기 힘든 용기 뚜껑 — 손 힘이 약하면 용기 뚜껑을 개봉하기 다소 힘듦</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>큰 알약 크기의 삼킴 부담 — 기존 제품 대비 알약 크기가 커서 한 번에 삼키기 다소 버거움</t>
+          <t>부담스러운 알약 크기 — 동봉된 알약 크기가 커서 삼키기 다소 불편함</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>강한 신맛의 자극 — 고함량 비타민C 분말 특성상 생각보다 신맛이 강해 먹을 때 찌릿함</t>
+          <t>강한 신맛 — 분말 제형 특성상 강한 신맛이 느껴짐</t>
         </is>
       </c>
     </row>
@@ -4488,14 +4453,14 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
+          <t>한끼통살</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
           <t>셀렉스</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>한끼통살</t>
-        </is>
-      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t>익스트림</t>
@@ -4503,12 +4468,12 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
           <t>알디콤</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
         </is>
       </c>
     </row>
@@ -4545,14 +4510,14 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
+          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
           <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>[한끼통살] 닭가슴살 순삭 10팩세트(소스통살5+닭가슴살볼5)</t>
-        </is>
-      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
@@ -4560,12 +4525,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
           <t>[단독] 알디콤Plus 숙취해소제 선물세트 (5포입x3개)</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
     </row>
@@ -4613,10 +4578,10 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>752</v>
@@ -4628,22 +4593,22 @@
         <v>60</v>
       </c>
       <c r="H19" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="I19" s="3" t="n">
         <v>217</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>69</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>248</v>
       </c>
       <c r="K19" s="3" t="n">
+        <v>903</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="L19" s="3" t="n">
-        <v>903</v>
-      </c>
-    </row>
-    <row r="20" ht="90" customHeight="1">
+    </row>
+    <row r="20" ht="60" customHeight="1">
       <c r="B20" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -4651,65 +4616,62 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>맛있는 소다맛 풍미 — 달지 않고 시원한 뽕따 소다 맛으로 거부감 없이 단독 섭취하기 좋음
-아이돌 포토카드 굿즈 — 아이돌 콜라보 포토카드 등 특별한 구성품이 포함되어 소장 가치가 높음</t>
+          <t>상큼하고 맛있는 풍미 — 블루베리요거트 및 소다 맛 등 상큼하게 먹기 좋음
+만족스러운 굿즈 구성 — 함께 제공되는 포토카드와 엽서 구성의 만족도가 높음</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>식후 소화 개선 효과 — 밀가루나 탄수화물 섭취 후 복용 시 속 더부룩함이 완화되고 편안해짐
-구수한 고구마맛 풍미 — 거부감 없는 구수한 고구마 맛이라 남녀노소 누구나 먹기 편함
-알찬 사은품 추가 증정 — 파로 곡물바와 파인키위효소 등 추가 증정품 구성이 푸짐함</t>
+          <t>편안한 소화 작용 — 식후 섭취 시 속이 편해지고 소화에 도움을 받음
+구수한 고구마 맛 — 구수한 고구마 풍미로 거부감 없이 맛있게 복용함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>우아한 선물 포장 — 플리츠백과 보자기 에디션 포장이 고급스러워 선물용으로 만족도가 높음
-거부감 없는 맛과 피로 개선 — 비린 맛 없이 달콤하게 마시기 좋으며 피로 완화에도 도움됨</t>
+          <t>고급스러운 포장 디자인 — 플리츠백 등 고급스러운 패키지 구성으로 만족스러움
+체감되는 피로 개선 — 꾸준히 마셨을 때 피로감이 덜 느껴짐</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 포만감 — 닭가슴살 특유의 물림 없이 맛있으며 한 개만 먹어도 포만감이 큼
-다채로운 맛과 보냉백 증정 — 30팩의 다양한 종류로 식단 구성이 좋고 증정 보냉백 디자인이 예쁨</t>
+          <t>뛰어난 맛과 포만감 — 한 개만 먹어도 포만감이 높고 소스가 맛있음
+다양한 식단 구성 — 종류가 다양하여 매일 질리지 않고 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>부드럽고 촉촉한 식감 — 퍽퍽하지 않고 육질이 매우 부드러우며 잡내가 나지 않아 질리지 않음
-알찬 구성과 뛰어난 가성비 — 다양한 종류의 닭가슴살과 간식을 할인된 저렴한 가격에 구매 가능함</t>
+          <t>부드럽고 촉촉한 식감 — 잡내가 없고 퍽퍽하지 않아 부드럽게 섭취 가능함
+우수한 가격 경쟁력 — 다양한 구성 대비 할인 가격이 저렴하여 가성비가 훌륭함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>비린내 없는 깔끔한 맛 — 프로틴 음료 특유의 텁텁함과 비린 맛 없이 진한 초코우유처럼 달콤함
-든든한 운동 후 단백질 보충 — 운동 직후 간편하게 마시기 좋으며 포만감이 오래 유지됨</t>
+          <t>쫄깃하고 촉촉한 식감 — 부드럽고 촉촉하여 다이어트 중에도 맛있게 섭취함
+전자레인지 조리 간편성 — 전자레인지로 쉽게 데워 먹을 수 있어 조리가 편함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>촉촉하고 쫄깃한 식감 — 퍽퍽함 없이 육질이 촉촉하고 부드러워 다이어트 중에도 맛있게 섭취함
-간편한 조리 및 섭취 — 전자레인지로 빠르게 조리 가능하며 한입 크기 볼 형태라 샐러드 곁들임에 좋음</t>
+          <t>비린 맛 없는 달콤함 — 단백질 특유의 비리고 텁텁한 맛이 없어 마시기 편함
+운동 후 든든한 포만감 — 운동 후 섭취 시 포만감을 주어 허기짐을 줄여줌</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>초고함량 활력 개선 효과 — 6,200mg 초고함량 아르기닌으로 운동 시 체력과 일상 활력 증진에 도움됨
-간편한 1일 1포 스틱 — 개별 포장된 액상 스틱 형태로 하루 한 포 간편하게 휴대하며 복용 가능함
-고급스러운 전용 쇼핑백 — 블랙과 레드의 깔끔한 포장과 전용 쇼핑백 증정으로 선물하기에 적합함</t>
+          <t>체감되는 활력 증진 — 섭취 후 피로감이 줄고 운동 퍼포먼스 및 체력 유지에 도움 됨
+고함량 스틱 포장 — 1포당 함량이 높고 개별 포장되어 휴대가 간편함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>확실한 숙취 해소 체감 — 음주 전후 복용 시 다음 날 아침 두통과 피로감이 덜해 숙취 해소에 탁월함
-휴대 편한 액상 스틱 — 물 없이 바로 짜먹을 수 있는 21ml 소용량 스틱이라 술자리 휴대에 적합함
-고급스러운 선물세트 패키지 — 보라색 쇼핑백과 리본 손잡이가 달린 포장으로 애주가 선물용으로 좋음</t>
+          <t>변비 완화 및 가벼움 — 복용 후 배변 활동이 원활해지고 몸이 가벼워짐
+저렴한 가격과 사은품 — 가격이 저렴하고 증정 과자 등 사은품 구성이 좋음</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>속 편안함 및 배변 도움 — 식후 복용 시 더부룩한 속이 편안해지고 배변 활동이 원활해짐을 느낌
-착한 가격과 스낵 증정 — 100포 대용량을 저렴하게 구매할 수 있고 저당 씬칩 사은품도 만족스러움</t>
+          <t>탁월한 숙취 해소 효과 — 음주 전후 섭취 시 다음 날 숙취와 피로감이 줄어듦
+고급스러운 선물 패키지 — 쇼핑백과 스틱 포장이 고급스러워 선물용으로 적합함</t>
         </is>
       </c>
     </row>
@@ -4723,33 +4685,33 @@
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>비싼 가격대 부담 — 제품 단가가 다소 높아 할인 행사가 없을 때는 구매 부담이 큼</t>
+          <t>부담스러운 가격 — 가격대가 다소 높아 할인 시에 주로 구매하게 됨</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>포장 불량 및 소스 누출 — 진공포장이 헐겁거나 배송 중 팩이 터져 소스가 새어 나오는 경우가 있음
-오배송 및 문의 응대 미흡 — 주문 구성과 다른 제품이 중복 배송되었으나 판매자 응대가 원활하지 않음</t>
+          <t>구성품 오배송 — 주문한 구성과 다르게 종류가 중복되거나 누락 배송됨
+제품 포장 파손 — 배송 중 포장이 터져 소스가 새거나 밀봉이 느슨함</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>선호 품목 제외 아쉬움 — 가장 선호하는 파우치형 그릴 제품이 이번 구성에 빠져 있어 아쉬움</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>다소 아쉬운 배송 속도 — 주문 후 출고 및 배송 도착까지 시간이 다소 걸림</t>
-        </is>
-      </c>
+          <t>선호 구성의 부재 — 가장 맛있는 파우치형 그릴 제품이 포함되지 않아 아쉬움</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>다소 느린 배송 — 주문 후 제품을 받아보기까지 배송 시간이 조금 걸림</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>약재 특유의 한약맛 — 쌍화탕이나 헛개 농축액 같은 씁쓸한 한약 맛이 돌아 입맛에 따라 호불호가 갈림</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>한약재 풍미의 호불호 — 쌍화탕이나 한약재 특유의 맛이 나 호불호가 갈릴 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="1" t="inlineStr">
@@ -4784,14 +4746,14 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
+          <t>20,900원</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
           <t>28,900원</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>20,900원</t>
-        </is>
-      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
           <t>43,900원</t>
@@ -4799,12 +4761,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
+          <t>21,900원</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
           <t>33,200원</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>21,900원</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4956,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5002,58 +4964,54 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대웅제약 철분 30정 30일분</t>
+          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000133&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580541&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260820/ahWGJ6KpupAlwxw7p3xm600000133_00_00ahWGJ6KpupAlwxw7p3xm.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250430/yuK2zGjcuX8RmMDP9k9P591580541_00_00yuK2zGjcuX8RmMDP9k9P.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>2501</v>
+        <v>1764</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>압도적인 가성비 — 한 달치 분량의 철분제를 부담 없는 저렴한 가격에 구매 가능함</t>
+          <t>착하고 저렴한 가격 — 가격 부담이 적고 브랜드 신뢰도가 높음</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>목넘김 편한 하루 한 알 — 알약 크기가 크지 않아 목넘김이 편하고 어지럼 완화에 도움을 줌</t>
+          <t>지속적인 눈 건강 관리 — 눈 피로감을 줄이고 꾸준히 눈 건강을 챙기기 좋음</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>개별 PTP 포장 아쉬움 — 블리스터 개별 포장 대신 통에 담긴 용기 형태로 나오면 좋겠음</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5061,12 +5019,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>종근당건강 브이퍼센트 멀티비타민 콜라겐샷 5포</t>
+          <t>대웅제약 알파CD ZERO 15포 15일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5076,34 +5034,34 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591591420&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000207&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250514/oMFpSUTevplZ5wvdXiLh591591420_00_00oMFpSUTevplZ5wvdXiLh.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251202/sucQSlMc1DA4dsj6Qff6600000207_00_00sucQSlMc1DA4dsj6Qff6.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>276</v>
+        <v>573</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>상큼한 오렌지맛 복합제형 — 오렌지 주스 맛 액상과 정제를 함께 먹는 이뮨 샷 형태로 복용이 즐거움</t>
+          <t>뛰어난 가성비 — 시중 판매가 대비 가격이 매우 저렴함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>믿을 수 있는 제약사 제조 — 종근당건강 브랜드 제품이라 품질에 대한 신뢰도가 높음</t>
+          <t>원활한 배변 활동 — 섭취 후 화장실을 원활하게 가게 되어 만족함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>다이소 기준 높은 가격대 — 5포에 5,000원으로 다이소 내 일반 건기식 제품 대비 개당 단가가 다소 높음</t>
+          <t>미미한 단기 효과 — 단기간 섭취 시 직접적인 효과 체감이 다소 미흡함</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -5112,7 +5070,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5120,62 +5078,58 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7 Days 슬립앤버닝 14정 7일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306284&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/e483TrUWUwCko9CBv1Da032306284_00_00e483TrUWUwCko9CBv1Da.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>132</v>
+        <v>2735</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>수면 질 개선 및 배변 도움 — 자기 전 복용 시 잠이 깊게 잘 오고 배변 활동이 원활해지는 느낌을 받음</t>
+          <t>편리한 휴대 및 복용 — 휴대하기 편하고 맛이 좋아 부담 없이 마심</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>체중 감량 보조 체감 — 꾸준히 복용하며 체중 앞자리가 줄어드는 감량 효과를 경험함</t>
+          <t>커피 대용 섭취 — 일상에서 커피 대신 간편하게 마시기 유용함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>다이어트 효과 체감 부족 — 수면 유도 효과에 비해 다이어트 감량 체감은 뚜렷하지 않음</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>한 달 누적 구매가 부담 — 7일분 소포장이라 4주분을 구매할 경우 비용이 2만 원대로 늘어남</t>
-        </is>
-      </c>
+          <t>아쉬운 커피 풍미 — 실제 커피 맛과는 차이가 있어 진한 맛이 아쉬움</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5183,7 +5137,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>종근당건강 혈행건강엔 rTG오메가3 비타민 ADE 30캡슐 30일분</t>
+          <t>종근당건강 브이퍼센트 멀티비타민 콜라겐샷 5포</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5198,34 +5152,34 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581111&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591591420&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260424/ryqqbn8htR0Ir3fAZcjp591581111_00_01ryqqbn8htR0Ir3fAZcjp.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250514/oMFpSUTevplZ5wvdXiLh591591420_00_00oMFpSUTevplZ5wvdXiLh.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>854</v>
+        <v>276</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>저렴한 가격의 알찬 구성 — 다이소에서 저렴하게 rTG 오메가3와 비타민 ADE를 한 번에 챙길 수 있음</t>
+          <t>상큼한 오렌지 맛 — 오렌지 주스 맛이 나 거부감 없이 맛있게 먹음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>쉬운 접근성과 재구매 — 온오프라인에서 부담 없이 장바구니에 담아 정기적으로 챙겨 먹기 좋음</t>
+          <t>편리한 이중 제형 — 액상과 정제를 함께 먹는 방식으로 복용이 편함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>단기간 내 변화 체감 미미 — 복용 초반에는 신체적인 큰 변화나 뚜렷한 염증 완화를 느끼기 어려움</t>
+          <t>다이소 내 높은 단가 — 다이소 판매 기준 개당 단가가 살짝 높은 편임</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -5234,7 +5188,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5242,12 +5196,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
+          <t>LG생활건강 이너뷰 콜라겐 더마스틱 7포</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5257,34 +5211,34 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580541&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953528&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250430/yuK2zGjcuX8RmMDP9k9P591580541_00_00yuK2zGjcuX8RmMDP9k9P.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/9Cz26kBHEVc4QcQuToeY994953528_00_009Cz26kBHEVc4QcQuToeY.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>1761</v>
+        <v>534</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>착한 가격의 눈 건강 관리 — 종근당건강의 루테인지아잔틴을 매우 합리적인 가격에 꾸준히 복용 가능함</t>
+          <t>뛰어난 가성비 — 브랜드 품질 대비 가격이 싸서 만족스러움</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>다이소몰 구매 편의성 — 오프라인 매장에 재고가 없는 제품을 온라인 몰에서 편리하게 구매함</t>
+          <t>신속한 배송 서비스 — 배송이 빠르고 상품 포장 상태가 양호함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>즉각적인 체감 효과 미미 — 복용 후 눈 피로나 시력 등에서 즉각적으로 눈에 띄는 변화는 체감하기 어려움</t>
+          <t>단기 효과 체감 부족 — 소량 구성 특성상 단기간 내 체감 효과를 알기 어려움</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -5293,7 +5247,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5301,7 +5255,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>자연관 스파이크컷 바나바잎＆카테킨 4병</t>
+          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5316,36 +5270,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627033&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762097&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260819/2NKz5YxykngJc58J5cja032627033_00_012NKz5YxykngJc58J5cja.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250807/jJGIxkBNqg0FzVjNiyoV901762097_00_01jJGIxkBNqg0FzVjNiyoV.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>350</v>
+        <v>1113</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>식후 소화 및 가스 완화 — 복용 시 복부 가스 참이나 소화 불편감을 덜어주는 느낌을 받음</t>
+          <t>과하지 않은 단맛 — 많이 달지 않고 적당한 풍미로 먹기 좋음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>거부감 없는 맛과 가성비 — 맛이 거부감 없이 먹기 편하며 저렴한 가격 대비 무난함</t>
+          <t>간편한 스틱 휴대 — 스틱 제형으로 들고 다니며 복용하기 편리함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>단기 섭취 시 효과 확인 한계 — 한두 번 섭취로는 뚜렷한 혈당 컷이나 다이어트 효과를 판단하기 어려움</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -5360,58 +5310,54 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 비타민B 30정 30일분</t>
+          <t>[신혜선 PICK] 동국제약 프라임도스 비타민B 맥스 30정 30일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000129&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911093&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5QghHD5oyZssCfnGZbzA600000129_00_005QghHD5oyZssCfnGZbzA.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260814/Q823T3m7aYDYd4gzOILy610911093_00_01Q823T3m7aYDYd4gzOILy.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2264</v>
+        <v>68</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>피로도 완화 체감 — 아침 복용 후 일상에서 느끼는 피로감이 줄어드는 느낌을 받음</t>
+          <t>높은 성분 함량 — 시중 비타민 B군 제품 대비 성분과 함량이 높음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>훌륭한 가성비와 편의성 — 가격 대비 구성이 매우 우수하며 정제 크기가 적당해 섭취하기 편함</t>
+          <t>부담 없는 가성비 — 저렴한 가격으로 고함량 영양제를 구매 가능함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>특유의 맛없는 냄새 — 비타민B 원료 특유의 맛없는 향이 올라와 삼킬 때 다소 신경 쓰임</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5419,12 +5365,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CJ 카무트 곡물과채콤부 화사 효소 10포 10일분</t>
+          <t>종근당건강 혈행건강엔 rTG오메가3 비타민 ADE 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CJ웰케어</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5434,28 +5380,28 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=139213437&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581111&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260623/2v2CuiCUbhEwDNpboF5B139213437_00_002v2CuiCUbhEwDNpboF5B.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260424/ryqqbn8htR0Ir3fAZcjp591581111_00_01ryqqbn8htR0Ir3fAZcjp.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1254</v>
+        <v>855</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>과식 후 소화 촉진 도움 — 식사 후나 과식한 날 섭취하면 더부룩한 속이 편안해지고 소화에 도움됨</t>
+          <t>착한 가격과 접근성 — 다이소에서 저렴한 가격으로 편하게 구매함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>휴대 편한 스틱형 포장 — 개별 포장되어 외식 후나 식후 언제 어디서나 간편하게 털어 넣기 좋음</t>
+          <t>일상적인 건강 관리 — 부담 없는 가격 덕분에 매일 꾸준히 챙겨 먹음</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -5466,7 +5412,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5474,7 +5420,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 24캡슐</t>
+          <t>안국약품 브이팩 남성용 올인원 멀티 비타민 7포</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5489,43 +5435,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982830&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=968235547&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/xCRETYTkHbPblUcjT18I611982830_00_00xCRETYTkHbPblUcjT18I.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/jgM8z9lj7cP7W5etxeXM968235547_00_00jgM8z9lj7cP7W5etxeXM.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1107</v>
+        <v>485</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>큼직한 캡슐 크기 만족 — 미니 캡슐과 달리 크기가 큼직하여 영양소를 든든하게 챙겨 먹는 느낌을 줌</t>
+          <t>간편한 올인원 복용 — 필요한 영양소를 한 번에 챙길 수 있어 편함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>친숙한 브랜드와 가성비 — 인지도 있는 안국약품 토비콤 제품을 가성비 있게 구매할 수 있음</t>
+          <t>지속적인 재구매 — 만족도가 높아 매장 방문 시 꾸준히 재구매함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>단기 복용 시 변화 체감 부족 — 노화 예방 목적으로 먹으나 복용 후 단기간 내 뚜렷한 눈 변화는 체감되지 않음</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5533,12 +5475,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 콜라겐 더마스틱 7포</t>
+          <t>자연관 이뮨 멀티비타민 미네랄 4병</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5548,37 +5490,41 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953528&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602124&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/9Cz26kBHEVc4QcQuToeY994953528_00_009Cz26kBHEVc4QcQuToeY.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251216/mSQXyRQCV8ORV8edPm4n613602124_00_01mSQXyRQCV8ORV8edPm4n.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>534</v>
+        <v>1894</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>맛있는 콜라겐 젤리스틱 — 비린 맛 없이 달콤하고 맛있어 간식처럼 쉽게 챙겨 먹을 수 있음</t>
+          <t>지칠 때 빠른 에너지 충전 — 피로감이 심할 때 섭취 시 에너지 충전에 도움이 됨</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>대기업 브랜드 대비 가성비 — LG생활건강 브랜드를 저렴한 가격에 부담 없이 체험해볼 수 있음</t>
+          <t>상큼한 과일 맛 — 패션후르츠 느낌의 상큼한 맛으로 마시기 좋음</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>적은 일수로 효과 한계 — 7포 구성이라 일주일 만에 가시적인 피부 개선 효과를 체감하긴 어려움</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>잦은 품절 및 재고 부족 — 인기가 많아 일시 품절이 자주 발생함</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>간혹 느껴지는 소화 부담 — 섭취 후 가끔 소화가 잘 안되는 느낌을 받음</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr"/>
     </row>
   </sheetData>
@@ -5692,52 +5638,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>루테인/눈건강</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
     </row>
@@ -5749,52 +5695,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>종근당건강</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>종근당건강</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>이너뷰 바이 리튠</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>자연관</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>종근당건강</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>안국약품</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>자연관</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>CJ웰케어</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>안국약품</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
     </row>
@@ -5806,52 +5752,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 철분 30정 30일분</t>
+          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>대웅제약 알파CD ZERO 15포 15일분</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>종근당건강 브이퍼센트 멀티비타민 콜라겐샷 5포</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿 푸응 7 Days 슬립앤버닝 14정 7일분</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>LG생활건강 이너뷰 콜라겐 더마스틱 7포</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[홍삼매니아] 자연관 홍삼정 에너타임 10포 10일분</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[신혜선 PICK] 동국제약 프라임도스 비타민B 맥스 30정 30일분</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>종근당건강 혈행건강엔 rTG오메가3 비타민 ADE 30캡슐 30일분</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강 눈건강엔 루테인지아잔틴</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>자연관 스파이크컷 바나바잎＆카테킨 4병</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 비타민B 30정 30일분</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>CJ 카무트 곡물과채콤부 화사 효소 10포 10일분</t>
-        </is>
-      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 24캡슐</t>
+          <t>안국약품 브이팩 남성용 올인원 멀티 비타민 7포</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 콜라겐 더마스틱 7포</t>
+          <t>자연관 이뮨 멀티비타민 미네랄 4병</t>
         </is>
       </c>
     </row>
@@ -5868,13 +5814,13 @@
         <v>4.8</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>4.8</v>
@@ -5889,7 +5835,7 @@
         <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -5899,34 +5845,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2501</v>
+        <v>1764</v>
       </c>
       <c r="D7" s="3" t="n">
+        <v>573</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>2735</v>
+      </c>
+      <c r="F7" s="3" t="n">
         <v>276</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>132</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>854</v>
-      </c>
       <c r="G7" s="3" t="n">
-        <v>1761</v>
+        <v>534</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>350</v>
+        <v>1113</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2264</v>
+        <v>68</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1254</v>
+        <v>855</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1107</v>
+        <v>485</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>534</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -5937,62 +5883,62 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>압도적인 가성비 — 한 달치 분량의 철분제를 부담 없는 저렴한 가격에 구매 가능함
-목넘김 편한 하루 한 알 — 알약 크기가 크지 않아 목넘김이 편하고 어지럼 완화에 도움을 줌</t>
+          <t>착하고 저렴한 가격 — 가격 부담이 적고 브랜드 신뢰도가 높음
+지속적인 눈 건강 관리 — 눈 피로감을 줄이고 꾸준히 눈 건강을 챙기기 좋음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>상큼한 오렌지맛 복합제형 — 오렌지 주스 맛 액상과 정제를 함께 먹는 이뮨 샷 형태로 복용이 즐거움
-믿을 수 있는 제약사 제조 — 종근당건강 브랜드 제품이라 품질에 대한 신뢰도가 높음</t>
+          <t>뛰어난 가성비 — 시중 판매가 대비 가격이 매우 저렴함
+원활한 배변 활동 — 섭취 후 화장실을 원활하게 가게 되어 만족함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>수면 질 개선 및 배변 도움 — 자기 전 복용 시 잠이 깊게 잘 오고 배변 활동이 원활해지는 느낌을 받음
-체중 감량 보조 체감 — 꾸준히 복용하며 체중 앞자리가 줄어드는 감량 효과를 경험함</t>
+          <t>편리한 휴대 및 복용 — 휴대하기 편하고 맛이 좋아 부담 없이 마심
+커피 대용 섭취 — 일상에서 커피 대신 간편하게 마시기 유용함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 가격의 알찬 구성 — 다이소에서 저렴하게 rTG 오메가3와 비타민 ADE를 한 번에 챙길 수 있음
-쉬운 접근성과 재구매 — 온오프라인에서 부담 없이 장바구니에 담아 정기적으로 챙겨 먹기 좋음</t>
+          <t>상큼한 오렌지 맛 — 오렌지 주스 맛이 나 거부감 없이 맛있게 먹음
+편리한 이중 제형 — 액상과 정제를 함께 먹는 방식으로 복용이 편함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>착한 가격의 눈 건강 관리 — 종근당건강의 루테인지아잔틴을 매우 합리적인 가격에 꾸준히 복용 가능함
-다이소몰 구매 편의성 — 오프라인 매장에 재고가 없는 제품을 온라인 몰에서 편리하게 구매함</t>
+          <t>뛰어난 가성비 — 브랜드 품질 대비 가격이 싸서 만족스러움
+신속한 배송 서비스 — 배송이 빠르고 상품 포장 상태가 양호함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>식후 소화 및 가스 완화 — 복용 시 복부 가스 참이나 소화 불편감을 덜어주는 느낌을 받음
-거부감 없는 맛과 가성비 — 맛이 거부감 없이 먹기 편하며 저렴한 가격 대비 무난함</t>
+          <t>과하지 않은 단맛 — 많이 달지 않고 적당한 풍미로 먹기 좋음
+간편한 스틱 휴대 — 스틱 제형으로 들고 다니며 복용하기 편리함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>피로도 완화 체감 — 아침 복용 후 일상에서 느끼는 피로감이 줄어드는 느낌을 받음
-훌륭한 가성비와 편의성 — 가격 대비 구성이 매우 우수하며 정제 크기가 적당해 섭취하기 편함</t>
+          <t>높은 성분 함량 — 시중 비타민 B군 제품 대비 성분과 함량이 높음
+부담 없는 가성비 — 저렴한 가격으로 고함량 영양제를 구매 가능함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>과식 후 소화 촉진 도움 — 식사 후나 과식한 날 섭취하면 더부룩한 속이 편안해지고 소화에 도움됨
-휴대 편한 스틱형 포장 — 개별 포장되어 외식 후나 식후 언제 어디서나 간편하게 털어 넣기 좋음</t>
+          <t>착한 가격과 접근성 — 다이소에서 저렴한 가격으로 편하게 구매함
+일상적인 건강 관리 — 부담 없는 가격 덕분에 매일 꾸준히 챙겨 먹음</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>큼직한 캡슐 크기 만족 — 미니 캡슐과 달리 크기가 큼직하여 영양소를 든든하게 챙겨 먹는 느낌을 줌
-친숙한 브랜드와 가성비 — 인지도 있는 안국약품 토비콤 제품을 가성비 있게 구매할 수 있음</t>
+          <t>간편한 올인원 복용 — 필요한 영양소를 한 번에 챙길 수 있어 편함
+지속적인 재구매 — 만족도가 높아 매장 방문 시 꾸준히 재구매함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 콜라겐 젤리스틱 — 비린 맛 없이 달콤하고 맛있어 간식처럼 쉽게 챙겨 먹을 수 있음
-대기업 브랜드 대비 가성비 — LG생활건강 브랜드를 저렴한 가격에 부담 없이 체험해볼 수 있음</t>
+          <t>지칠 때 빠른 에너지 충전 — 피로감이 심할 때 섭취 시 에너지 충전에 도움이 됨
+상큼한 과일 맛 — 패션후르츠 느낌의 상큼한 맛으로 마시기 좋음</t>
         </is>
       </c>
     </row>
@@ -6002,51 +5948,35 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>개별 PTP 포장 아쉬움 — 블리스터 개별 포장 대신 통에 담긴 용기 형태로 나오면 좋겠음</t>
-        </is>
-      </c>
+      <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>다이소 기준 높은 가격대 — 5포에 5,000원으로 다이소 내 일반 건기식 제품 대비 개당 단가가 다소 높음</t>
+          <t>미미한 단기 효과 — 단기간 섭취 시 직접적인 효과 체감이 다소 미흡함</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>다이어트 효과 체감 부족 — 수면 유도 효과에 비해 다이어트 감량 체감은 뚜렷하지 않음
-한 달 누적 구매가 부담 — 7일분 소포장이라 4주분을 구매할 경우 비용이 2만 원대로 늘어남</t>
+          <t>아쉬운 커피 풍미 — 실제 커피 맛과는 차이가 있어 진한 맛이 아쉬움</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>단기간 내 변화 체감 미미 — 복용 초반에는 신체적인 큰 변화나 뚜렷한 염증 완화를 느끼기 어려움</t>
+          <t>다이소 내 높은 단가 — 다이소 판매 기준 개당 단가가 살짝 높은 편임</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>즉각적인 체감 효과 미미 — 복용 후 눈 피로나 시력 등에서 즉각적으로 눈에 띄는 변화는 체감하기 어려움</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>단기 섭취 시 효과 확인 한계 — 한두 번 섭취로는 뚜렷한 혈당 컷이나 다이어트 효과를 판단하기 어려움</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>특유의 맛없는 냄새 — 비타민B 원료 특유의 맛없는 향이 올라와 삼킬 때 다소 신경 쓰임</t>
-        </is>
-      </c>
+          <t>단기 효과 체감 부족 — 소량 구성 특성상 단기간 내 체감 효과를 알기 어려움</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>단기 복용 시 변화 체감 부족 — 노화 예방 목적으로 먹으나 복용 후 단기간 내 뚜렷한 눈 변화는 체감되지 않음</t>
-        </is>
-      </c>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>적은 일수로 효과 한계 — 7포 구성이라 일주일 만에 가시적인 피부 개선 효과를 체감하긴 어려움</t>
+          <t>잦은 품절 및 재고 부족 — 인기가 많아 일시 품절이 자주 발생함
+간혹 느껴지는 소화 부담 — 섭취 후 가끔 소화가 잘 안되는 느낌을 받음</t>
         </is>
       </c>
     </row>
@@ -6058,7 +5988,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -6068,27 +5998,27 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -6282,7 +6212,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6290,27 +6220,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26,800원</t>
+          <t>35,800원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246272&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627206ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6333,43 +6263,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>35,800원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>549</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364591ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>체지방과 장 건강 동시 케어 — 체지방 감소와 장내 환경 개선을 한 번에 챙길 수 있는 이중기능성이라 유용함</t>
+          <t>원활한 배변 및 클렌즈 — 섭취 후 화장실을 잘 가며 더부룩한 뱃살 완화에 도움 됨</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>상큼한 맛있는 요거트맛 — 상큼한 요거트 맛 분말이라 물 없이도 하루 한 포 맛있게 섭취 가능함</t>
+          <t>부담 없는 체지방 관리 — 굶지 않고 일상에서 꾸준히 체지방을 관리하기 용이함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -6380,7 +6306,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6388,40 +6314,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246271&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627107ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>149</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>간편한 이너뷰티 섭취 — 피부 건강과 속광 관리를 위해 부담 없이 챙기기 좋은 복숭아 맛 콜라겐임</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -6431,7 +6349,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6439,45 +6357,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>리쥬란 이너닷 DNA 글로우 젤리(단품/기획)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>리쥬란</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20,900원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000258641&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025864120ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1096</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>탱글하고 맛있는 젤리 — 청포도 사과 맛의 쫀득한 젤리 제형이라 간식처럼 맛있게 섭취할 수 있음</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>안심 배합과 휴대 편의 — 일본산 원료 및 부형제를 배제하였고 낱개 포장으로 외출 시 휴대가 용이함</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -6486,7 +6392,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6494,43 +6400,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>생활약속</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>16,200원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>17106</v>
+        <v>8343</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>탁월한 얼굴 붓기 완화 — 야식 섭취나 촬영 등 중요한 일정 전 복용 시 얼굴 땡땡함과 붓기 완화에 도움됨</t>
+          <t>매력적인 기획 굿즈 — 키링 및 포토카드 등 기획 증정품의 만족도가 높음</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>목넘김 편한 미니환 — 환 크기가 매우 작아 목에 걸림 없이 물과 함께 수월하게 넘길 수 있음</t>
+          <t>넉넉한 2개월 용량 — 60캡슐 구성으로 두 달 동안 여유 있게 복용 가능함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -6541,7 +6447,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6549,33 +6455,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>아이힐 비너스 질유산균 30캡슐 (+6캡슐) 증량 기획</t>
+          <t>리쥬란 이너닷 DNA 글로우 젤리(단품/기획)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>아이힐</t>
+          <t>리쥬란</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>28,400원</t>
+          <t>20,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000217101&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000258641&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021710167ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025864120ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1098</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>상큼한 청포도 사과 맛 — 청포도 사과 맛 젤리로 간식처럼 맛있게 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>편리한 휴대 및 알찬 구성 — 낱개 포장으로 휴대가 편하며 증정 수량이 알참</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -6592,27 +6510,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>16,200원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -6627,7 +6545,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6635,45 +6553,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
+          <t>[TWS 띠부씰 증정] 미에로화이바 브이캔디 20정 기획</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>미에로화이바</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>59,000원</t>
+          <t>9,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249509&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000268343&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024950901ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026834303ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>403</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>질과 장 더블 케어 — 여성 질 건강과 장 건강을 한 번에 케어할 수 있어 실용적임</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>목넘김 편한 소형 캡슐 — 캡슐 크기가 작아 목 넘김이 수월하며 복용을 중단했을 때 역체감이 큼</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -6682,7 +6592,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6690,45 +6600,37 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[김우빈PICK] 아임비타 멀티비타민 이뮨샷 12입 (+포차코 메쉬백) (12일분)</t>
+          <t>닥터아돌 베이비 FeD 유산균 30포 (30일분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>아임비타</t>
+          <t>닥터아돌</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>29,660원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249166&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000231629&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A000000249166125ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023162914ko.png?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>11053</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>귀엽고 실용적인 증정 굿즈 — 포차코 메쉬백 사은품이 수영이나 헬스 시 세면도구 가방으로 유용함</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>맛있는 액상과 편한 정제 — 알약 크기가 적당하고 하단 액상이 진한 비타민 음료처럼 맛있음</t>
-        </is>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
@@ -6737,7 +6639,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6745,43 +6647,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587421ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>24899</v>
+        <v>5262</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>아침 공복 장 건강 개선 — 아침 기상 후 물과 함께 복용 시 배변 활동과 면역력 관리에 효과적임</t>
+          <t>상큼하고 쫀득한 맛 — 레몬라임 등 상큼한 풍미와 쫀득한 식감으로 맛이 우수함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1일 1캡슐 간편한 섭취 — 하루 한 알만 챙기면 되는 소형 캡슐이며 더블 기획으로 두 달간 넉넉히 복용함</t>
+          <t>물 없이 간편한 구미 — 물 없이 언제 어디서나 간식처럼 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -6900,7 +6802,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -6910,42 +6812,42 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
     </row>
@@ -6957,52 +6859,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>리쥬란</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>생활약속</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>아이힐</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>멜라메이트</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>미에로화이바</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>아임비타</t>
+          <t>닥터아돌</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>올더베러</t>
         </is>
       </c>
     </row>
@@ -7014,52 +6916,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>리쥬란 이너닷 DNA 글로우 젤리(단품/기획)</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>아이힐 비너스 질유산균 30캡슐 (+6캡슐) 증량 기획</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
+          <t>[TWS 띠부씰 증정] 미에로화이바 브이캔디 20정 기획</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[김우빈PICK] 아임비타 멀티비타민 이뮨샷 12입 (+포차코 메쉬백) (12일분)</t>
+          <t>닥터아돌 베이비 FeD 유산균 30포 (30일분)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
     </row>
@@ -7070,28 +6972,24 @@
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="3" t="n">
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -7101,28 +6999,24 @@
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="n">
-        <v>549</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>149</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>1096</v>
-      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="n">
-        <v>17106</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr"/>
+        <v>8343</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1098</v>
+      </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>403</v>
+        <v>20</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>11053</v>
+        <v>23</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>24899</v>
+        <v>5262</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
@@ -7134,45 +7028,31 @@
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>체지방과 장 건강 동시 케어 — 체지방 감소와 장내 환경 개선을 한 번에 챙길 수 있는 이중기능성이라 유용함
-상큼한 맛있는 요거트맛 — 상큼한 요거트 맛 분말이라 물 없이도 하루 한 포 맛있게 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>간편한 이너뷰티 섭취 — 피부 건강과 속광 관리를 위해 부담 없이 챙기기 좋은 복숭아 맛 콜라겐임</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>탱글하고 맛있는 젤리 — 청포도 사과 맛의 쫀득한 젤리 제형이라 간식처럼 맛있게 섭취할 수 있음
-안심 배합과 휴대 편의 — 일본산 원료 및 부형제를 배제하였고 낱개 포장으로 외출 시 휴대가 용이함</t>
-        </is>
-      </c>
+          <t>원활한 배변 및 클렌즈 — 섭취 후 화장실을 잘 가며 더부룩한 뱃살 완화에 도움 됨
+부담 없는 체지방 관리 — 굶지 않고 일상에서 꾸준히 체지방을 관리하기 용이함</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>탁월한 얼굴 붓기 완화 — 야식 섭취나 촬영 등 중요한 일정 전 복용 시 얼굴 땡땡함과 붓기 완화에 도움됨
-목넘김 편한 미니환 — 환 크기가 매우 작아 목에 걸림 없이 물과 함께 수월하게 넘길 수 있음</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr"/>
+          <t>매력적인 기획 굿즈 — 키링 및 포토카드 등 기획 증정품의 만족도가 높음
+넉넉한 2개월 용량 — 60캡슐 구성으로 두 달 동안 여유 있게 복용 가능함</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>상큼한 청포도 사과 맛 — 청포도 사과 맛 젤리로 간식처럼 맛있게 먹기 좋음
+편리한 휴대 및 알찬 구성 — 낱개 포장으로 휴대가 편하며 증정 수량이 알참</t>
+        </is>
+      </c>
       <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>질과 장 더블 케어 — 여성 질 건강과 장 건강을 한 번에 케어할 수 있어 실용적임
-목넘김 편한 소형 캡슐 — 캡슐 크기가 작아 목 넘김이 수월하며 복용을 중단했을 때 역체감이 큼</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>귀엽고 실용적인 증정 굿즈 — 포차코 메쉬백 사은품이 수영이나 헬스 시 세면도구 가방으로 유용함
-맛있는 액상과 편한 정제 — 알약 크기가 적당하고 하단 액상이 진한 비타민 음료처럼 맛있음</t>
-        </is>
-      </c>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>아침 공복 장 건강 개선 — 아침 기상 후 물과 함께 복용 시 배변 활동과 면역력 관리에 효과적임
-1일 1캡슐 간편한 섭취 — 하루 한 알만 챙기면 되는 소형 캡슐이며 더블 기획으로 두 달간 넉넉히 복용함</t>
+          <t>상큼하고 쫀득한 맛 — 레몬라임 등 상큼한 풍미와 쫀득한 식감으로 맛이 우수함
+물 없이 간편한 구미 — 물 없이 언제 어디서나 간식처럼 챙겨 먹기 편함</t>
         </is>
       </c>
     </row>
@@ -7201,52 +7081,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>26,800원</t>
+          <t>35,800원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>35,800원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
           <t>20,900원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>16,200원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>28,400원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>16,900원</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>59,000원</t>
+          <t>9,900원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26,900원</t>
+          <t>29,660원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>10,900원</t>
         </is>
       </c>
     </row>
@@ -7376,19 +7256,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>27.5</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
         <v>4</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -7398,19 +7278,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -7420,10 +7300,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
@@ -7432,13 +7312,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -7448,32 +7328,32 @@
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -7482,42 +7362,42 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -7526,7 +7406,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B9" t="n">
